--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -42,9 +42,6 @@
     <t>모든 스탯 증가</t>
   </si>
   <si>
-    <t>대시 횟수 증가</t>
-  </si>
-  <si>
     <t>공격력 증가, 공격속도 감소 및 쿨타임 증가</t>
   </si>
   <si>
@@ -707,27 +704,18 @@
     <t>적 처치 시 적 폭발</t>
   </si>
   <si>
-    <t>적 피격시 확률로 폭탄 부착</t>
-  </si>
-  <si>
     <t>적 피격시 확률로 지뢰 설치</t>
   </si>
   <si>
     <t>피격시 확률적으로 공격받은방향으로 범위데미지</t>
   </si>
   <si>
-    <t>피격시 확률로 폭죽 발사</t>
-  </si>
-  <si>
     <t>피격시 발동형 효과 랜덤 발동</t>
   </si>
   <si>
     <t>일정시간마다 캐릭터 주변 지속피해 원 생성</t>
   </si>
   <si>
-    <t>일정시간마다 방패가 생성되어 플레이어와 공전</t>
-  </si>
-  <si>
     <t>일정시간마다 주변적 정지</t>
   </si>
   <si>
@@ -746,19 +734,84 @@
     <t>공격시 확률적으로 투사체 발사</t>
   </si>
   <si>
+    <t>캐릭터 교체시 범위데미지</t>
+  </si>
+  <si>
+    <t>벽에 튕기는 공격 물체 발사</t>
+  </si>
+  <si>
+    <t>일정시간마다 적이 있는곳에 장판</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정시간마다 캐릭터 주변 적 슬로우</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>횟수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 처치 시 확률로 폭탄 부착</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 시 확률로 폭죽 발사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>공격시 확률적으로 되돌아오는 투사체 발사</t>
-  </si>
-  <si>
-    <t>캐릭터 교체시 범위데미지</t>
-  </si>
-  <si>
-    <t>바라보는 방향으로 일정 범위만큼 적 슬로우</t>
-  </si>
-  <si>
-    <t>벽에 튕기는 공격 물체 발사</t>
-  </si>
-  <si>
-    <t>일정시간마다 적이 있는곳에 장판</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>방패가 생성되어 플레이어 주변 투사체 방어</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1208,22 +1261,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" t="s">
-        <v>24</v>
-      </c>
       <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" t="s">
-        <v>28</v>
-      </c>
       <c r="F1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1342,7 +1395,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
@@ -1355,7 +1408,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="4">
         <v>10</v>
@@ -1368,7 +1421,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="4">
         <v>30</v>
@@ -1385,7 +1438,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="4">
         <v>25</v>
@@ -1402,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="4">
         <v>1</v>
@@ -1415,7 +1468,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="4">
         <v>1</v>
@@ -1428,7 +1481,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="4">
         <v>3</v>
@@ -1445,7 +1498,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" s="4">
         <v>30</v>
@@ -1460,7 +1513,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="4">
         <v>20</v>
@@ -1475,7 +1528,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" s="4">
         <v>20</v>
@@ -1490,7 +1543,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="4">
         <v>30</v>
@@ -1505,7 +1558,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" s="4">
         <v>30</v>
@@ -1518,7 +1571,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22" s="4">
         <v>50</v>
@@ -1531,7 +1584,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" s="4">
         <v>4</v>
@@ -1544,7 +1597,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" s="4">
         <v>1</v>
@@ -1557,7 +1610,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="4">
         <v>50</v>
@@ -1570,7 +1623,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="4">
         <v>20</v>
@@ -1583,7 +1636,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" s="4">
         <v>1</v>
@@ -1596,7 +1649,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C28" s="4">
         <v>0.5</v>
@@ -1609,7 +1662,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C29" s="4">
         <v>1</v>
@@ -1622,7 +1675,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C30" s="4">
         <v>1</v>
@@ -1635,10 +1688,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" s="6">
         <v>5</v>
+      </c>
+      <c r="D31">
+        <v>0.05</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1646,205 +1702,203 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="C33" s="6"/>
+    </row>
+    <row r="34" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+      <c r="C34" s="6"/>
+    </row>
+    <row r="35" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+      <c r="C35" s="6"/>
+    </row>
+    <row r="36" spans="1:4" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C36" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D36">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+      <c r="C37" s="6"/>
+    </row>
+    <row r="38" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C38" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D38">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C39" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C40" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C41" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C42" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C43" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C44" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C45" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C46" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C47" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C49">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -1427,7 +1427,7 @@
         <v>30</v>
       </c>
       <c r="D12" s="4">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="5">
         <v>5</v>

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\GstarPrototype\Assets\01KDH\Scripts\Item\ItemDB\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="360" yWindow="45" windowWidth="28035" windowHeight="12570"/>
   </bookViews>
@@ -737,88 +742,89 @@
     <t>캐릭터 교체시 범위데미지</t>
   </si>
   <si>
-    <t>벽에 튕기는 공격 물체 발사</t>
-  </si>
-  <si>
     <t>일정시간마다 적이 있는곳에 장판</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>횟수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 처치 시 확률로 폭탄 부착</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 시 확률로 폭죽 발사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격시 확률적으로 되돌아오는 투사체 발사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>방패가 생성되어 플레이어 주변 투사체 방어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>일정시간마다 캐릭터 주변 적 슬로우</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>횟수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>증가</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적 처치 시 확률로 폭탄 부착</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격 시 확률로 폭죽 발사</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격시 확률적으로 되돌아오는 투사체 발사</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>방패가 생성되어 플레이어 주변 투사체 방어</t>
+    <t>일정시간마다 데미지를 입히는 조각을 발사</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -961,6 +967,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -1008,7 +1017,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1043,7 +1052,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1395,7 +1404,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
@@ -1713,9 +1722,11 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="6"/>
+        <v>49</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="34" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
@@ -1740,7 +1751,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C36" s="6">
         <v>5</v>
@@ -1777,7 +1788,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C39" s="6">
         <v>1</v>
@@ -1788,7 +1799,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40" s="6">
         <v>10</v>
@@ -1835,7 +1846,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="6">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1865,7 +1876,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C47" s="6">
         <v>5</v>
@@ -1884,7 +1895,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C49">
         <v>10</v>
@@ -1898,7 +1909,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>47</v>
+        <v>54</v>
+      </c>
+      <c r="C50" s="6">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -797,10 +797,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>적 처치 시 확률로 폭탄 부착</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>공격 시 확률로 폭죽 발사</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -818,6 +814,10 @@
   </si>
   <si>
     <t>일정시간마다 데미지를 입히는 조각을 발사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정 시간마다 수리검 소환</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1722,10 +1722,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C33" s="6">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1751,7 +1751,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" s="6">
         <v>5</v>
@@ -1788,7 +1788,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C39" s="6">
         <v>1</v>
@@ -1876,7 +1876,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47" s="6">
         <v>5</v>
@@ -1895,7 +1895,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>10</v>
@@ -1909,7 +1909,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50" s="6">
         <v>2</v>

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -1754,7 +1754,7 @@
         <v>49</v>
       </c>
       <c r="C36" s="6">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>0.15</v>

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\GstarPrototype\Assets\01KDH\Scripts\Item\ItemDB\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="360" yWindow="45" windowWidth="28035" windowHeight="12570"/>
   </bookViews>
@@ -730,15 +725,6 @@
     <t>공격시 확률적으로 연쇄번개</t>
   </si>
   <si>
-    <t>공격시 확률적으로 범위피격(여래신장)</t>
-  </si>
-  <si>
-    <t>공격시 확률적으로 범위 장판</t>
-  </si>
-  <si>
-    <t>공격시 확률적으로 투사체 발사</t>
-  </si>
-  <si>
     <t>캐릭터 교체시 범위데미지</t>
   </si>
   <si>
@@ -797,10 +783,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>공격 시 확률로 폭죽 발사</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>공격시 확률적으로 되돌아오는 투사체 발사</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -813,18 +795,34 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>일정시간마다 데미지를 입히는 조각을 발사</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>일정 시간마다 수리검 소환</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 시 랜덤한 적에게 범위형 폭죽 발사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격시 확률적으로 적에게 칼바람 부착</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격시 확률적으로 실드 발사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격시 확률적으로 회오리 발사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정시간마다 데미지를 입히는 별가루 발사</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1017,7 +1015,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1052,7 +1050,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1404,7 +1402,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
@@ -1700,10 +1698,13 @@
         <v>34</v>
       </c>
       <c r="C31" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="D31">
         <v>5</v>
       </c>
-      <c r="D31">
-        <v>0.05</v>
+      <c r="E31">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1714,21 +1715,27 @@
         <v>35</v>
       </c>
       <c r="C32" s="6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.2</v>
+      </c>
+      <c r="D32">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C33" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="D33">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -1737,7 +1744,7 @@
       </c>
       <c r="C34" s="6"/>
     </row>
-    <row r="35" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -1746,21 +1753,24 @@
       </c>
       <c r="C35" s="6"/>
     </row>
-    <row r="36" spans="1:4" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C36" s="6">
-        <v>100</v>
+        <v>0.25</v>
       </c>
       <c r="D36">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.04</v>
+      </c>
+      <c r="E36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -1769,7 +1779,7 @@
       </c>
       <c r="C37" s="6"/>
     </row>
-    <row r="38" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -1780,32 +1790,41 @@
         <v>10</v>
       </c>
       <c r="D38">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.2</v>
+      </c>
+      <c r="E38">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C39" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C40" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D40">
+        <v>0.3</v>
+      </c>
+      <c r="E40">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -1816,7 +1835,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -1827,7 +1846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -1835,84 +1854,123 @@
         <v>42</v>
       </c>
       <c r="C43" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.4</v>
+      </c>
+      <c r="D43">
+        <v>0.1</v>
+      </c>
+      <c r="E43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C44" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.2</v>
+      </c>
+      <c r="D44">
+        <v>0.05</v>
+      </c>
+      <c r="E44">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C45" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.35</v>
+      </c>
+      <c r="D45">
+        <v>0.05</v>
+      </c>
+      <c r="E45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C46" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.25</v>
+      </c>
+      <c r="D46">
+        <v>0.1</v>
+      </c>
+      <c r="E46">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C47" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C49">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D49">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.25</v>
+      </c>
+      <c r="E49">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C50" s="6">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D50">
+        <v>0.1</v>
+      </c>
+      <c r="E50">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -16,22 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
-  <si>
-    <t>스킬 쿨타임 감소</t>
-  </si>
-  <si>
-    <t>데미지 증가</t>
-  </si>
-  <si>
-    <t>공격속도 증가</t>
-  </si>
-  <si>
-    <t>이동속도 증가</t>
-  </si>
-  <si>
-    <t>최대 체력 증가</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>치명타 데미지 증가</t>
   </si>
@@ -42,45 +27,9 @@
     <t>모든 스탯 증가</t>
   </si>
   <si>
-    <t>공격력 증가, 공격속도 감소 및 쿨타임 증가</t>
-  </si>
-  <si>
-    <t>스킬 충전 횟수 증가</t>
-  </si>
-  <si>
-    <t>궁극기 스킬 충전 횟수 증가</t>
-  </si>
-  <si>
-    <t>토템 무시하고 진행시 스탯 증가</t>
-  </si>
-  <si>
-    <t>최대 체력 대폭 감소 공격력 대폭 증가</t>
-  </si>
-  <si>
-    <t>최대 체력 대폭 감소, 체력 흡혈 능력 흭득 및 대폭 증가</t>
-  </si>
-  <si>
-    <t>최대 체력 대폭 증가, 이동 속도 대폭 감소</t>
-  </si>
-  <si>
-    <t>대시 사용 불가, 이동 속도 대폭 증가</t>
-  </si>
-  <si>
-    <t>스킬 사용시 확률로 다른 스킬 쿨타임 감소</t>
-  </si>
-  <si>
     <t>일정 시간마다 체력 자동회복</t>
   </si>
   <si>
-    <t>적 처치 시 최대체력 증가 최대치 존재</t>
-  </si>
-  <si>
-    <t>적 처치 시 최대공격속도 증가 최대치 존재</t>
-  </si>
-  <si>
-    <t>적 처치 시 최대공격력 증가 최대치 존재</t>
-  </si>
-  <si>
     <t>부활</t>
   </si>
   <si>
@@ -92,6 +41,258 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>itemVariable</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>itemVariable2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>itemVariable3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>itemVariable4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 처치시 체력회복오브 드랍</t>
+  </si>
+  <si>
+    <t>적 처치 시 적 폭발</t>
+  </si>
+  <si>
+    <t>적 피격시 확률로 지뢰 설치</t>
+  </si>
+  <si>
+    <t>피격시 확률적으로 공격받은방향으로 범위데미지</t>
+  </si>
+  <si>
+    <t>피격시 발동형 효과 랜덤 발동</t>
+  </si>
+  <si>
+    <t>일정시간마다 캐릭터 주변 지속피해 원 생성</t>
+  </si>
+  <si>
+    <t>일정시간마다 주변적 정지</t>
+  </si>
+  <si>
+    <t>일정시간마다 짧은 무적</t>
+  </si>
+  <si>
+    <t>공격시 확률적으로 연쇄번개</t>
+  </si>
+  <si>
+    <t>캐릭터 교체시 범위데미지</t>
+  </si>
+  <si>
+    <t>일정시간마다 적이 있는곳에 장판</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격시 확률적으로 되돌아오는 투사체 발사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>방패가 생성되어 플레이어 주변 투사체 방어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정시간마다 캐릭터 주변 적 슬로우</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정 시간마다 수리검 소환</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 시 랜덤한 적에게 범위형 폭죽 발사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격시 확률적으로 적에게 칼바람 부착</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격시 확률적으로 실드 발사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격시 확률적으로 회오리 발사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정시간마다 데미지를 입히는 별가루 발사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격속도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 10% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스킬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쿨타임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감소</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데미지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -109,6 +310,63 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve"> 25 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격속도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 20% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
@@ -119,6 +377,127 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쿨타임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이동속도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
       <t>감소</t>
     </r>
     <r>
@@ -138,6 +517,437 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
+      <t>골드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>획득</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 50 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 100 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최대체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최대공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 10% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>text1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>text2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>text3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>text4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
       <t>공격속도</t>
     </r>
     <r>
@@ -147,6 +957,117 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve"> 20% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쿨타임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감소</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
@@ -157,6 +1078,25 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 150 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
       <t>증가</t>
     </r>
     <r>
@@ -166,6 +1106,25 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
@@ -176,35 +1135,16 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>쿨타임</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t>속도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
     </r>
     <r>
       <rPr>
@@ -216,606 +1156,6 @@
       </rPr>
       <t>감소</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>itemVariable</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>itemVariable2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>itemVariable3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>범위</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>증가</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최대</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>체력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대폭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>감소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>골드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>획득</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>증가</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>치명타</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>확률</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>고정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>치명타</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>추가데미지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대폭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상승</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>일정시간마다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최대체력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>랜덤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>변경</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 50% ~ 200%</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>일정시간마다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>데미지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>랜덤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>변경</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최종데미지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 20% ~ 500%</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>itemVariable4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적 처치시 체력회복오브 드랍</t>
-  </si>
-  <si>
-    <t>적 처치 시 적 폭발</t>
-  </si>
-  <si>
-    <t>적 피격시 확률로 지뢰 설치</t>
-  </si>
-  <si>
-    <t>피격시 확률적으로 공격받은방향으로 범위데미지</t>
-  </si>
-  <si>
-    <t>피격시 발동형 효과 랜덤 발동</t>
-  </si>
-  <si>
-    <t>일정시간마다 캐릭터 주변 지속피해 원 생성</t>
-  </si>
-  <si>
-    <t>일정시간마다 주변적 정지</t>
-  </si>
-  <si>
-    <t>일정시간마다 짧은 무적</t>
-  </si>
-  <si>
-    <t>공격시 확률적으로 연쇄번개</t>
-  </si>
-  <si>
-    <t>캐릭터 교체시 범위데미지</t>
-  </si>
-  <si>
-    <t>일정시간마다 적이 있는곳에 장판</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>대시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>횟수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>증가</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격시 확률적으로 되돌아오는 투사체 발사</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>방패가 생성되어 플레이어 주변 투사체 방어</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>일정시간마다 캐릭터 주변 적 슬로우</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>일정 시간마다 수리검 소환</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격 시 랜덤한 적에게 범위형 폭죽 발사</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격시 확률적으로 적에게 칼바람 부착</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격시 확률적으로 실드 발사</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격시 확률적으로 회오리 발사</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>일정시간마다 데미지를 입히는 별가루 발사</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1259,352 +1599,399 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="55.625" customWidth="1"/>
     <col min="3" max="6" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C2" s="4">
-        <v>8</v>
+        <v>0.02</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G2" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="C3" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G3" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C4" s="4">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="5"/>
-    </row>
-    <row r="5" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G4" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C5" s="4">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G5" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C6" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G6" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C7" s="4">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G7" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C8" s="4">
         <v>5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="5"/>
-    </row>
-    <row r="9" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G8" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C9" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D9" s="4">
-        <v>3</v>
+        <v>0.15</v>
       </c>
       <c r="E9" s="5">
         <v>3</v>
       </c>
       <c r="F9" s="1">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I9" s="1">
+        <v>3</v>
+      </c>
+      <c r="J9" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C10" s="4">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="4">
-        <v>10</v>
-      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C12" s="4">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D12" s="4">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E12" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="G12" s="1">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C13" s="4">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D13" s="4">
-        <v>10</v>
-      </c>
-      <c r="E13" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0.6</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="G13" s="1">
+        <v>15</v>
+      </c>
+      <c r="H13" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="C14" s="4">
-        <v>1</v>
-      </c>
-      <c r="D14" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0.05</v>
+      </c>
       <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G14" s="1">
+        <v>15</v>
+      </c>
+      <c r="H14" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>13</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="4">
-        <v>1</v>
-      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>14</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="4">
-        <v>3</v>
-      </c>
-      <c r="D16" s="4">
-        <v>2</v>
-      </c>
-      <c r="E16" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="3"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C17" s="4">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D17" s="4">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G17" s="1">
+        <v>50</v>
+      </c>
+      <c r="H17" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C18" s="4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D18" s="4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>17</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="4">
-        <v>20</v>
-      </c>
-      <c r="D19" s="4">
-        <v>15</v>
-      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C20" s="4">
+        <v>150</v>
+      </c>
+      <c r="D20" s="4">
         <v>30</v>
       </c>
-      <c r="D20" s="4">
-        <v>12</v>
-      </c>
       <c r="E20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G20" s="1">
+        <v>150</v>
+      </c>
+      <c r="H20" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>19</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="4">
-        <v>30</v>
-      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>20</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="4">
-        <v>50</v>
-      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>21</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="4">
-        <v>4</v>
-      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C24" s="4">
         <v>1</v>
@@ -1612,77 +1999,65 @@
       <c r="D24" s="4"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>23</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="4">
-        <v>50</v>
-      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>24</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="4">
-        <v>20</v>
-      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C27" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>26</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="4">
-        <v>0.5</v>
-      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>27</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C29" s="4">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:5" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>28</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C30" s="4">
         <v>1</v>
@@ -1690,12 +2065,12 @@
       <c r="D30" s="4"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C31" s="6">
         <v>0.05</v>
@@ -1706,13 +2081,19 @@
       <c r="E31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G31">
+        <v>5</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C32" s="6">
         <v>0.2</v>
@@ -1720,13 +2101,19 @@
       <c r="D32">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G32">
+        <v>20</v>
+      </c>
+      <c r="H32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="C33" s="6">
         <v>5</v>
@@ -1734,31 +2121,40 @@
       <c r="D33">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="H33">
+        <v>10</v>
+      </c>
+      <c r="I33">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C34" s="6"/>
     </row>
-    <row r="35" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C35" s="6"/>
     </row>
-    <row r="36" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="C36" s="6">
         <v>0.25</v>
@@ -1769,22 +2165,31 @@
       <c r="E36">
         <v>10</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G36">
+        <v>10</v>
+      </c>
+      <c r="H36">
+        <v>25</v>
+      </c>
+      <c r="I36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C37" s="6"/>
     </row>
-    <row r="38" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C38" s="6">
         <v>10</v>
@@ -1795,24 +2200,33 @@
       <c r="E38">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G38">
+        <v>10</v>
+      </c>
+      <c r="H38">
+        <v>50</v>
+      </c>
+      <c r="I38">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C39" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C40" s="6">
         <v>10</v>
@@ -1823,35 +2237,44 @@
       <c r="E40">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G40">
+        <v>10</v>
+      </c>
+      <c r="H40">
+        <v>30</v>
+      </c>
+      <c r="I40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C41" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="C42" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="C43" s="6">
         <v>0.4</v>
@@ -1862,13 +2285,22 @@
       <c r="E43">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G43">
+        <v>10</v>
+      </c>
+      <c r="H43">
+        <v>50</v>
+      </c>
+      <c r="I43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C44" s="6">
         <v>0.2</v>
@@ -1879,13 +2311,22 @@
       <c r="E44">
         <v>20</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G44">
+        <v>20</v>
+      </c>
+      <c r="H44">
+        <v>20</v>
+      </c>
+      <c r="I44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C45" s="6">
         <v>0.35</v>
@@ -1896,13 +2337,22 @@
       <c r="E45">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G45">
+        <v>10</v>
+      </c>
+      <c r="H45">
+        <v>35</v>
+      </c>
+      <c r="I45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C46" s="6">
         <v>0.25</v>
@@ -1913,13 +2363,22 @@
       <c r="E46">
         <v>20</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G46">
+        <v>20</v>
+      </c>
+      <c r="H46">
+        <v>25</v>
+      </c>
+      <c r="I46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C47" s="6">
         <v>0</v>
@@ -1931,20 +2390,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C49">
         <v>15</v>
@@ -1955,13 +2414,22 @@
       <c r="E49">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G49">
+        <v>15</v>
+      </c>
+      <c r="H49">
+        <v>25</v>
+      </c>
+      <c r="I49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C50" s="6">
         <v>3</v>
@@ -1971,6 +2439,15 @@
       </c>
       <c r="E50">
         <v>0.03</v>
+      </c>
+      <c r="G50">
+        <v>3</v>
+      </c>
+      <c r="H50">
+        <v>10</v>
+      </c>
+      <c r="I50">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>치명타 데미지 증가</t>
   </si>
@@ -78,9 +78,6 @@
     <t>일정시간마다 주변적 정지</t>
   </si>
   <si>
-    <t>일정시간마다 짧은 무적</t>
-  </si>
-  <si>
     <t>공격시 확률적으로 연쇄번개</t>
   </si>
   <si>
@@ -1155,6 +1152,117 @@
         <charset val="129"/>
       </rPr>
       <t>감소</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>초당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재생</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>골드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보너스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> +10%</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1626,16 +1734,16 @@
         <v>10</v>
       </c>
       <c r="G1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" t="s">
         <v>42</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>43</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>44</v>
-      </c>
-      <c r="J1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1643,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="4">
         <v>0.02</v>
@@ -1659,7 +1767,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="4">
         <v>5</v>
@@ -1675,7 +1783,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="4">
         <v>0.3</v>
@@ -1691,7 +1799,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="4">
         <v>15</v>
@@ -1707,7 +1815,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" s="4">
         <v>25</v>
@@ -1787,7 +1895,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" s="4">
         <v>0.1</v>
@@ -1802,17 +1910,32 @@
       <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="B11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.05</v>
+      </c>
       <c r="E11" s="5"/>
+      <c r="G11" s="1">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" s="4">
         <v>25</v>
@@ -1838,7 +1961,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" s="4">
         <v>15</v>
@@ -1859,7 +1982,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="4">
         <v>15</v>
@@ -1879,10 +2002,20 @@
       <c r="A15" s="2">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
+      <c r="B15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0.1</v>
+      </c>
       <c r="D15" s="4"/>
       <c r="E15" s="5"/>
+      <c r="G15" s="1">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
@@ -1898,7 +2031,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="4">
         <v>50</v>
@@ -1919,7 +2052,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" s="4">
         <v>30</v>
@@ -1943,7 +2076,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="4">
         <v>150</v>
@@ -2022,7 +2155,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C27" s="4">
         <v>0.5</v>
@@ -2044,7 +2177,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" s="4">
         <v>0.05</v>
@@ -2113,7 +2246,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C33" s="6">
         <v>5</v>
@@ -2154,7 +2287,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C36" s="6">
         <v>0.25</v>
@@ -2215,9 +2348,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39" s="6">
+        <v>22</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="G39">
+        <v>3</v>
+      </c>
+      <c r="H39">
         <v>1</v>
       </c>
     </row>
@@ -2226,7 +2363,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" s="6">
         <v>10</v>
@@ -2262,19 +2399,14 @@
       <c r="A42" s="2">
         <v>40</v>
       </c>
-      <c r="B42" t="s">
-        <v>18</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1</v>
-      </c>
+      <c r="C42" s="6"/>
     </row>
     <row r="43" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C43" s="6">
         <v>0.4</v>
@@ -2300,7 +2432,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C44" s="6">
         <v>0.2</v>
@@ -2326,7 +2458,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C45" s="6">
         <v>0.35</v>
@@ -2352,7 +2484,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46" s="6">
         <v>0.25</v>
@@ -2378,7 +2510,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C47" s="6">
         <v>0</v>
@@ -2395,7 +2527,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2403,7 +2535,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C49">
         <v>15</v>
@@ -2429,7 +2561,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C50" s="6">
         <v>3</v>

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -457,6 +457,44 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
+      <t>공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 50 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
       <t>최대</t>
     </r>
     <r>
@@ -485,6 +523,678 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve"> 100 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최대체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처치</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최대공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 10% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>text1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>text2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>text3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>text4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격속도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 20% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쿨타임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감소</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 150 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감소</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>초당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재생</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>골드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보너스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> +10%</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve"> 30 </t>
     </r>
     <r>
@@ -533,7 +1243,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>획득</t>
+      <t>보상</t>
     </r>
     <r>
       <rPr>
@@ -552,707 +1262,6 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>증가</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>공격력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 50 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>증가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최대</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>체력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 100 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>감소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>적</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>처치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최대체력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>증가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>적</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>처치</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최대공격력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>증가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>공격력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 10% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>증가</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>text1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>text2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>text3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>text4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>공격력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 15 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>감소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>공격속도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 20% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>증가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t/>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>공격력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 15 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>감소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>쿨타임</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 5% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>감소</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최대</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>체력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 150 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>증가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>속도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">30 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>감소</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>초당</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>체력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>재생</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>골드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
       <t>보너스</t>
     </r>
     <r>
@@ -1262,7 +1271,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> +10%</t>
+      <t xml:space="preserve"> +20%</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1734,16 +1743,16 @@
         <v>10</v>
       </c>
       <c r="G1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>42</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>43</v>
-      </c>
-      <c r="J1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1895,7 +1904,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="4">
         <v>0.1</v>
@@ -1911,7 +1920,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
@@ -1961,7 +1970,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="4">
         <v>15</v>
@@ -1982,7 +1991,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="4">
         <v>15</v>
@@ -2003,7 +2012,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" s="4">
         <v>0.1</v>
@@ -2031,7 +2040,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="4">
         <v>50</v>
@@ -2052,15 +2061,21 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C18" s="4">
         <v>30</v>
       </c>
       <c r="D18" s="4">
-        <v>25</v>
+        <v>0.2</v>
       </c>
       <c r="E18" s="5"/>
+      <c r="G18" s="1">
+        <v>30</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="19" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
@@ -2076,7 +2091,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" s="4">
         <v>150</v>
@@ -2155,7 +2170,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C27" s="4">
         <v>0.5</v>
@@ -2177,7 +2192,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C29" s="4">
         <v>0.05</v>

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -2035,7 +2035,7 @@
       <c r="D16" s="4"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -2076,8 +2076,11 @@
       <c r="H18" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I18" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -2086,7 +2089,7 @@
       <c r="D19" s="4"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -2107,7 +2110,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -2116,7 +2119,7 @@
       <c r="D21" s="4"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -2125,7 +2128,7 @@
       <c r="D22" s="4"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -2134,7 +2137,7 @@
       <c r="D23" s="4"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -2147,7 +2150,7 @@
       <c r="D24" s="4"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2156,7 +2159,7 @@
       <c r="D25" s="4"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -2165,7 +2168,7 @@
       <c r="D26" s="4"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -2178,7 +2181,7 @@
       <c r="D27" s="4"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -2187,7 +2190,7 @@
       <c r="D28" s="4"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -2200,7 +2203,7 @@
       <c r="D29" s="4"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -2213,7 +2216,7 @@
       <c r="D30" s="4"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -2236,7 +2239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -2384,7 +2387,7 @@
         <v>10</v>
       </c>
       <c r="D40">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="E40">
         <v>0.05</v>
@@ -2393,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="H40">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I40">
         <v>5</v>
@@ -2556,7 +2559,7 @@
         <v>15</v>
       </c>
       <c r="D49">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="E49">
         <v>0.05</v>
@@ -2565,7 +2568,7 @@
         <v>15</v>
       </c>
       <c r="H49">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I49">
         <v>5</v>

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -1933,10 +1933,10 @@
         <v>10</v>
       </c>
       <c r="H11" s="1">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="I11" s="1">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -2176,10 +2176,13 @@
         <v>37</v>
       </c>
       <c r="C27" s="4">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="5"/>
+      <c r="G27" s="1">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="28" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
@@ -2198,10 +2201,13 @@
         <v>38</v>
       </c>
       <c r="C29" s="4">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="5"/>
+      <c r="G29" s="1">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="30" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -1797,7 +1797,9 @@
       <c r="C4" s="4">
         <v>0.3</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="4">
+        <v>0.1</v>
+      </c>
       <c r="E4" s="5"/>
       <c r="G4" s="1">
         <v>10</v>
@@ -1827,12 +1829,12 @@
         <v>33</v>
       </c>
       <c r="C6" s="4">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="5"/>
       <c r="G6" s="1">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1978,7 +1980,9 @@
       <c r="D13" s="4">
         <v>0.6</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="5">
+        <v>0.2</v>
+      </c>
       <c r="G13" s="1">
         <v>15</v>
       </c>
@@ -2064,14 +2068,14 @@
         <v>49</v>
       </c>
       <c r="C18" s="4">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="D18" s="4">
         <v>0.2</v>
       </c>
       <c r="E18" s="5"/>
       <c r="G18" s="1">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="H18" s="1">
         <v>20</v>
@@ -2097,14 +2101,14 @@
         <v>46</v>
       </c>
       <c r="C20" s="4">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="D20" s="4">
         <v>30</v>
       </c>
       <c r="E20" s="5"/>
       <c r="G20" s="1">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H20" s="1">
         <v>30</v>
@@ -2176,12 +2180,12 @@
         <v>37</v>
       </c>
       <c r="C27" s="4">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="5"/>
       <c r="G27" s="1">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -1779,12 +1779,12 @@
         <v>32</v>
       </c>
       <c r="C3" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="5"/>
       <c r="G3" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>치명타 데미지 증가</t>
   </si>
@@ -1273,6 +1273,10 @@
       </rPr>
       <t xml:space="preserve"> +20%</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                      </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1716,14 +1720,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="55.625" customWidth="1"/>
     <col min="3" max="6" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1755,7 +1759,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -1771,7 +1775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1786,8 +1790,11 @@
       <c r="G3" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K3" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1805,7 +1812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1821,7 +1828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1837,7 +1844,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1853,7 +1860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1869,7 +1876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1901,7 +1908,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1917,7 +1924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1928,20 +1935,20 @@
         <v>1</v>
       </c>
       <c r="D11" s="4">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="E11" s="5"/>
       <c r="G11" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1967,7 +1974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1990,7 +1997,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -2011,7 +2018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -2030,7 +2037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>14</v>
       </c>

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -2187,12 +2187,15 @@
         <v>37</v>
       </c>
       <c r="C27" s="4">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="5"/>
       <c r="G27" s="1">
-        <v>0.5</v>
+        <v>0.25</v>
+      </c>
+      <c r="H27" s="1">
+        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2218,6 +2221,9 @@
       <c r="E29" s="5"/>
       <c r="G29" s="1">
         <v>0.1</v>
+      </c>
+      <c r="H29" s="1">
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -1893,7 +1893,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="G9" s="1">
         <v>10</v>
@@ -1905,7 +1905,7 @@
         <v>3</v>
       </c>
       <c r="J9" s="1">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">

--- a/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
+++ b/Assets/01KDH/Scripts/Item/ItemDB/ItemDB.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\GstarPrototype\Assets\01KDH\Scripts\Item\ItemDB\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="45" windowWidth="28035" windowHeight="12570"/>
+    <workbookView xWindow="360" yWindow="48" windowWidth="28032" windowHeight="12576"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1283,7 +1288,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1476,7 +1481,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1511,7 +1516,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1721,13 +1726,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K50"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="55.625" customWidth="1"/>
-    <col min="3" max="6" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="55.59765625" customWidth="1"/>
+    <col min="3" max="6" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1759,7 +1764,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -1775,7 +1780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1794,7 +1799,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1812,7 +1817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1828,7 +1833,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1844,7 +1849,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1860,7 +1865,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1876,7 +1881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1908,7 +1913,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1924,7 +1929,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1948,7 +1953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1974,7 +1979,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1997,7 +2002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -2018,7 +2023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -2037,7 +2042,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -2046,7 +2051,7 @@
       <c r="D16" s="4"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -2067,7 +2072,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -2091,7 +2096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -2100,7 +2105,7 @@
       <c r="D19" s="4"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -2121,7 +2126,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -2130,7 +2135,7 @@
       <c r="D21" s="4"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -2139,7 +2144,7 @@
       <c r="D22" s="4"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -2148,7 +2153,7 @@
       <c r="D23" s="4"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -2161,7 +2166,7 @@
       <c r="D24" s="4"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2170,7 +2175,7 @@
       <c r="D25" s="4"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -2179,7 +2184,7 @@
       <c r="D26" s="4"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -2198,7 +2203,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -2207,7 +2212,7 @@
       <c r="D28" s="4"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -2226,7 +2231,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -2239,7 +2244,7 @@
       <c r="D30" s="4"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -2247,7 +2252,7 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -2259,10 +2264,13 @@
         <v>5</v>
       </c>
       <c r="H31">
+        <v>2</v>
+      </c>
+      <c r="I31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -2282,7 +2290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -2305,7 +2313,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -2314,7 +2322,7 @@
       </c>
       <c r="C34" s="6"/>
     </row>
-    <row r="35" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -2323,7 +2331,7 @@
       </c>
       <c r="C35" s="6"/>
     </row>
-    <row r="36" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -2349,7 +2357,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -2358,7 +2366,7 @@
       </c>
       <c r="C37" s="6"/>
     </row>
-    <row r="38" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -2384,7 +2392,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -2399,7 +2407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -2425,7 +2433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -2436,13 +2444,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>40</v>
       </c>
       <c r="C42" s="6"/>
     </row>
-    <row r="43" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -2468,7 +2476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -2494,7 +2502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -2520,7 +2528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -2546,7 +2554,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
         <v>45</v>
       </c>
@@ -2563,7 +2571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
         <v>46</v>
       </c>
@@ -2571,7 +2579,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
         <v>47</v>
       </c>
@@ -2597,7 +2605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>48</v>
       </c>
@@ -2633,7 +2641,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2643,7 +2651,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
